--- a/server/data.xlsx
+++ b/server/data.xlsx
@@ -64,8 +64,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -397,10 +398,801 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetData/>
+  <dimension ref="A1:EA2"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>created_at</v>
+      </c>
+      <c r="C1" t="str">
+        <v>TagNo</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Item Name</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Quantity</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Project</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Plate MATERIAL</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Flange MATERIAL</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Flange Type</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Piece Type</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Weld Type</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Holder Type</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Line_Size</v>
+      </c>
+      <c r="N1" t="str">
+        <v>Size in NPS OR DN</v>
+      </c>
+      <c r="O1" t="str">
+        <v>Flange Schedule</v>
+      </c>
+      <c r="P1" t="str">
+        <v>Pipe Wall Thk</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>Rating</v>
+      </c>
+      <c r="R1" t="str">
+        <v>RJ HOLDER MATERIAL</v>
+      </c>
+      <c r="S1" t="str">
+        <v>Drain/Vent</v>
+      </c>
+      <c r="T1" t="str">
+        <v>Smooth Finish</v>
+      </c>
+      <c r="U1" t="str">
+        <v>Serration</v>
+      </c>
+      <c r="V1" t="str">
+        <v>Stellite</v>
+      </c>
+      <c r="W1" t="str">
+        <v>Fluid/Service_Name</v>
+      </c>
+      <c r="X1" t="str">
+        <v>Service Discription</v>
+      </c>
+      <c r="Y1" t="str">
+        <v>Service Type</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>Calculation Standard</v>
+      </c>
+      <c r="AA1" t="str">
+        <v>Flow Element Type</v>
+      </c>
+      <c r="AB1" t="str">
+        <v>Flow Rate Unit</v>
+      </c>
+      <c r="AC1" t="str">
+        <v>Flow Rate Minimum</v>
+      </c>
+      <c r="AD1" t="str">
+        <v>Flow Rate Maximum</v>
+      </c>
+      <c r="AE1" t="str">
+        <v>Flow Rate Normal</v>
+      </c>
+      <c r="AF1" t="str">
+        <v>Flow Rate at FullScale</v>
+      </c>
+      <c r="AG1" t="str">
+        <v>Tapping</v>
+      </c>
+      <c r="AH1" t="str">
+        <v>Multi Hole</v>
+      </c>
+      <c r="AI1" t="str">
+        <v>Pipe Material</v>
+      </c>
+      <c r="AJ1" t="str">
+        <v>Pressure Unit</v>
+      </c>
+      <c r="AK1" t="str">
+        <v>Temp Unit</v>
+      </c>
+      <c r="AL1" t="str">
+        <v>Viscosity Unit</v>
+      </c>
+      <c r="AM1" t="str">
+        <v>Density Unit</v>
+      </c>
+      <c r="AN1" t="str">
+        <v>Density_Calc_Method</v>
+      </c>
+      <c r="AO1" t="str">
+        <v>MolecularWeight_Customer</v>
+      </c>
+      <c r="AP1" t="str">
+        <v>Compressibility_atFlow_Customer</v>
+      </c>
+      <c r="AQ1" t="str">
+        <v>Compressibility_atBase_Customer</v>
+      </c>
+      <c r="AR1" t="str">
+        <v>Gas Name</v>
+      </c>
+      <c r="AS1" t="str">
+        <v>Base Pressure</v>
+      </c>
+      <c r="AT1" t="str">
+        <v>Upstream Pressure</v>
+      </c>
+      <c r="AU1" t="str">
+        <v>Base_Temperature</v>
+      </c>
+      <c r="AV1" t="str">
+        <v>Operating_Temperature</v>
+      </c>
+      <c r="AW1" t="str">
+        <v>Vapour_Pressure</v>
+      </c>
+      <c r="AX1" t="str">
+        <v>Density_at_Base_Customer</v>
+      </c>
+      <c r="AY1" t="str">
+        <v>Density_at_Flow_Customer</v>
+      </c>
+      <c r="AZ1" t="str">
+        <v>Viscosity_Customer</v>
+      </c>
+      <c r="BA1" t="str">
+        <v>IsentropicExponent_Customer</v>
+      </c>
+      <c r="BB1" t="str">
+        <v>DP Unit</v>
+      </c>
+      <c r="BC1" t="str">
+        <v>DP at Full Scale</v>
+      </c>
+      <c r="BD1" t="str">
+        <v>Design Pressure Discription</v>
+      </c>
+      <c r="BE1" t="str">
+        <v>Design Pressure</v>
+      </c>
+      <c r="BF1" t="str">
+        <v>Design Temp Discription</v>
+      </c>
+      <c r="BG1" t="str">
+        <v>Design Temp</v>
+      </c>
+      <c r="BH1" t="str">
+        <v>Flange Standard</v>
+      </c>
+      <c r="BI1" t="str">
+        <v>Plate Thk Customer</v>
+      </c>
+      <c r="BJ1" t="str">
+        <v>Spare Plate Required</v>
+      </c>
+      <c r="BK1" t="str">
+        <v>Stud/Nut</v>
+      </c>
+      <c r="BL1" t="str">
+        <v>Gasket</v>
+      </c>
+      <c r="BM1" t="str">
+        <v>JackBolt</v>
+      </c>
+      <c r="BN1" t="str">
+        <v>Packing_Cost_Manual</v>
+      </c>
+      <c r="BO1" t="str">
+        <v>Accessories</v>
+      </c>
+      <c r="BP1" t="str">
+        <v>Accessories_Amt</v>
+      </c>
+      <c r="BQ1" t="str">
+        <v>IBR</v>
+      </c>
+      <c r="BR1" t="str">
+        <v>IBR_Amt_Manual</v>
+      </c>
+      <c r="BS1" t="str">
+        <v>Nace</v>
+      </c>
+      <c r="BT1" t="str">
+        <v>Nace_Type</v>
+      </c>
+      <c r="BU1" t="str">
+        <v>Nace_Percent</v>
+      </c>
+      <c r="BV1" t="str">
+        <v>Calibration</v>
+      </c>
+      <c r="BW1" t="str">
+        <v>CalibrationAmt_Manual</v>
+      </c>
+      <c r="BX1" t="str">
+        <v>Freight_Required</v>
+      </c>
+      <c r="BY1" t="str">
+        <v>Freight_Amt_Manual</v>
+      </c>
+      <c r="BZ1" t="str">
+        <v>Special_Requirement</v>
+      </c>
+      <c r="CA1" t="str">
+        <v>Special_Requirement_Amt</v>
+      </c>
+      <c r="CB1" t="str">
+        <v>OFA Tap Orientation</v>
+      </c>
+      <c r="CC1" t="str">
+        <v>FNA Tap Orientation</v>
+      </c>
+      <c r="CD1" t="str">
+        <v>Venturi Tap Orientation</v>
+      </c>
+      <c r="CE1" t="str">
+        <v>Plug_Material</v>
+      </c>
+      <c r="CF1" t="str">
+        <v>Pressure_Tap_Angle</v>
+      </c>
+      <c r="CG1" t="str">
+        <v>JackBold_Position</v>
+      </c>
+      <c r="CH1" t="str">
+        <v>ItemCode_Heading</v>
+      </c>
+      <c r="CI1" t="str">
+        <v>ItemCode</v>
+      </c>
+      <c r="CJ1" t="str">
+        <v>TestSchedule</v>
+      </c>
+      <c r="CK1" t="str">
+        <v>FNA Pipe Machining Required</v>
+      </c>
+      <c r="CL1" t="str">
+        <v>FNA Pipe Machined Cost</v>
+      </c>
+      <c r="CM1" t="str">
+        <v>FNA Total Assy. Length</v>
+      </c>
+      <c r="CN1" t="str">
+        <v>FNA Upstream Length</v>
+      </c>
+      <c r="CO1" t="str">
+        <v>FNA Pipe Length Show to Customer</v>
+      </c>
+      <c r="CP1" t="str">
+        <v>FNA Pipe Length Customer</v>
+      </c>
+      <c r="CQ1" t="str">
+        <v>Chamfer</v>
+      </c>
+      <c r="CR1" t="str">
+        <v>ØD1</v>
+      </c>
+      <c r="CS1" t="str">
+        <v>Adapter Rating</v>
+      </c>
+      <c r="CT1" t="str">
+        <v>Flow Nozzle Holding Ring Material</v>
+      </c>
+      <c r="CU1" t="str">
+        <v>Flow Nozzle Material</v>
+      </c>
+      <c r="CV1" t="str">
+        <v>Nipple Material</v>
+      </c>
+      <c r="CW1" t="str">
+        <v>Nipple Size</v>
+      </c>
+      <c r="CX1" t="str">
+        <v>Nipple Schedule</v>
+      </c>
+      <c r="CY1" t="str">
+        <v>Nipple Quantity</v>
+      </c>
+      <c r="CZ1" t="str">
+        <v>Venturi Throat Material</v>
+      </c>
+      <c r="DA1" t="str">
+        <v>Cyllinder Material</v>
+      </c>
+      <c r="DB1" t="str">
+        <v>Cone Material</v>
+      </c>
+      <c r="DC1" t="str">
+        <v>Piezometer RIng Material</v>
+      </c>
+      <c r="DD1" t="str">
+        <v>End Flange Standard</v>
+      </c>
+      <c r="DE1" t="str">
+        <v>End Flange Type</v>
+      </c>
+      <c r="DF1" t="str">
+        <v>End Flange Material</v>
+      </c>
+      <c r="DG1" t="str">
+        <v>End Flange Rating</v>
+      </c>
+      <c r="DH1" t="str">
+        <v>No of End Flange</v>
+      </c>
+      <c r="DI1" t="str">
+        <v>Adapter Material</v>
+      </c>
+      <c r="DJ1" t="str">
+        <v>No. of Tapping 1</v>
+      </c>
+      <c r="DK1" t="str">
+        <v>Tap Size 1</v>
+      </c>
+      <c r="DL1" t="str">
+        <v>No. of Tapping 2</v>
+      </c>
+      <c r="DM1" t="str">
+        <v>Tap Size 2</v>
+      </c>
+      <c r="DN1" t="str">
+        <v>Companion Flange Required</v>
+      </c>
+      <c r="DO1" t="str">
+        <v>Tapping Flange</v>
+      </c>
+      <c r="DP1" t="str">
+        <v>Tapping Flange Size</v>
+      </c>
+      <c r="DQ1" t="str">
+        <v>PilotTube Type</v>
+      </c>
+      <c r="DR1" t="str">
+        <v>Duct Inside Width</v>
+      </c>
+      <c r="DS1" t="str">
+        <v>Duct Outside Width</v>
+      </c>
+      <c r="DT1" t="str">
+        <v>Duct Inside Height</v>
+      </c>
+      <c r="DU1" t="str">
+        <v>Duct Outside Height</v>
+      </c>
+      <c r="DV1" t="str">
+        <v>PitotTube Probe Material</v>
+      </c>
+      <c r="DW1" t="str">
+        <v>Pitot Tube Type</v>
+      </c>
+      <c r="DX1" t="str">
+        <v>Pitot End Support</v>
+      </c>
+      <c r="DY1" t="str">
+        <v>Clamping Condition</v>
+      </c>
+      <c r="DZ1" t="str">
+        <v>Pitot Tube End Connection Material</v>
+      </c>
+      <c r="EA1" t="str">
+        <v>Pitot Tube Sleeve Material</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>46177.4190346875</v>
+      </c>
+      <c r="C2" t="str">
+        <v>FE-101A</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Restriction Orifice Assembly</v>
+      </c>
+      <c r="E2" t="str">
+        <v>1.0</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Refinery Expansion Phase 3</v>
+      </c>
+      <c r="G2" t="str">
+        <v>SS316</v>
+      </c>
+      <c r="H2" t="str">
+        <v>A105 Carbon Steel</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Weld Neck</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Single Piece</v>
+      </c>
+      <c r="K2" t="str">
+        <v>Butt Weld</v>
+      </c>
+      <c r="L2" t="str">
+        <v>Integral Carrier</v>
+      </c>
+      <c r="M2" t="str">
+        <v>8 in</v>
+      </c>
+      <c r="N2" t="str">
+        <v>DN 200</v>
+      </c>
+      <c r="O2" t="str">
+        <v>STD</v>
+      </c>
+      <c r="P2" t="str">
+        <v>8.18 mm</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>300#</v>
+      </c>
+      <c r="R2" t="str">
+        <v>None</v>
+      </c>
+      <c r="S2" t="str">
+        <v>Drain Only</v>
+      </c>
+      <c r="T2" t="str">
+        <v>125-250 AARH</v>
+      </c>
+      <c r="U2" t="str">
+        <v>Standard Serrated</v>
+      </c>
+      <c r="V2" t="str">
+        <v>No</v>
+      </c>
+      <c r="W2" t="str">
+        <v>Crude Oil Stream</v>
+      </c>
+      <c r="X2" t="str">
+        <v>Hydrocarbon Processing Loop</v>
+      </c>
+      <c r="Y2" t="str">
+        <v>Liquid Phase</v>
+      </c>
+      <c r="Z2" t="str">
+        <v>ISO 5167</v>
+      </c>
+      <c r="AA2" t="str">
+        <v>Orifice Plate</v>
+      </c>
+      <c r="AB2" t="str">
+        <v>kg/h</v>
+      </c>
+      <c r="AC2" t="str">
+        <v>12000.0</v>
+      </c>
+      <c r="AD2" t="str">
+        <v>45000.0</v>
+      </c>
+      <c r="AE2" t="str">
+        <v>32000.0</v>
+      </c>
+      <c r="AF2" t="str">
+        <v>50000.0</v>
+      </c>
+      <c r="AG2" t="str">
+        <v>Flange Taps</v>
+      </c>
+      <c r="AH2" t="str">
+        <v>No</v>
+      </c>
+      <c r="AI2" t="str">
+        <v>A106-B</v>
+      </c>
+      <c r="AJ2" t="str">
+        <v>kg/cm2(g)</v>
+      </c>
+      <c r="AK2" t="str">
+        <v>Celsius</v>
+      </c>
+      <c r="AL2" t="str">
+        <v>cP</v>
+      </c>
+      <c r="AM2" t="str">
+        <v>kg/m3</v>
+      </c>
+      <c r="AN2" t="str">
+        <v>AGA8 Real Gas Method</v>
+      </c>
+      <c r="AO2" t="str">
+        <v>44.01</v>
+      </c>
+      <c r="AP2" t="str">
+        <v>0.985</v>
+      </c>
+      <c r="AQ2" t="str">
+        <v>0.992</v>
+      </c>
+      <c r="AR2" t="str">
+        <v>Associated Gas Mix</v>
+      </c>
+      <c r="AS2" t="str">
+        <v>1.033</v>
+      </c>
+      <c r="AT2" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="AU2" t="str">
+        <v>15.0</v>
+      </c>
+      <c r="AV2" t="str">
+        <v>65.0</v>
+      </c>
+      <c r="AW2" t="str">
+        <v>0.45</v>
+      </c>
+      <c r="AX2" t="str">
+        <v>1.22</v>
+      </c>
+      <c r="AY2" t="str">
+        <v>850.5</v>
+      </c>
+      <c r="AZ2" t="str">
+        <v>0.32</v>
+      </c>
+      <c r="BA2" t="str">
+        <v>1.32</v>
+      </c>
+      <c r="BB2" t="str">
+        <v>mmH2O</v>
+      </c>
+      <c r="BC2" t="str">
+        <v>2500.0</v>
+      </c>
+      <c r="BD2" t="str">
+        <v>Max Operating Limit</v>
+      </c>
+      <c r="BE2" t="str">
+        <v>19.2</v>
+      </c>
+      <c r="BF2" t="str">
+        <v>Max Structural Design</v>
+      </c>
+      <c r="BG2" t="str">
+        <v>120.0</v>
+      </c>
+      <c r="BH2" t="str">
+        <v>ASME B16.5</v>
+      </c>
+      <c r="BI2" t="str">
+        <v>6.35</v>
+      </c>
+      <c r="BJ2" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="BK2" t="str">
+        <v>A193-B7 / A194-2H</v>
+      </c>
+      <c r="BL2" t="str">
+        <v>Spiral Wound SS316</v>
+      </c>
+      <c r="BM2" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="BN2" t="str">
+        <v>150.0</v>
+      </c>
+      <c r="BO2" t="str">
+        <v>Hex Plugs Installed</v>
+      </c>
+      <c r="BP2" t="str">
+        <v>75.0</v>
+      </c>
+      <c r="BQ2" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="BR2" t="str">
+        <v>250.0</v>
+      </c>
+      <c r="BS2" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="BT2" t="str">
+        <v>Class 1</v>
+      </c>
+      <c r="BU2" t="str">
+        <v>0.15</v>
+      </c>
+      <c r="BV2" t="str">
+        <v>Factory Calibrated</v>
+      </c>
+      <c r="BW2" t="str">
+        <v>500.0</v>
+      </c>
+      <c r="BX2" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="BY2" t="str">
+        <v>350.0</v>
+      </c>
+      <c r="BZ2" t="str">
+        <v>NACE MR0175 Compliance Certification Mandatory</v>
+      </c>
+      <c r="CA2" t="str">
+        <v>0.0</v>
+      </c>
+      <c r="CB2" t="str">
+        <v>90 Degrees Top</v>
+      </c>
+      <c r="CC2" t="str">
+        <v>None</v>
+      </c>
+      <c r="CD2" t="str">
+        <v>None</v>
+      </c>
+      <c r="CE2" t="str">
+        <v>SS316</v>
+      </c>
+      <c r="CF2" t="str">
+        <v>45.0</v>
+      </c>
+      <c r="CG2" t="str">
+        <v>Top Vertical</v>
+      </c>
+      <c r="CH2" t="str">
+        <v>IC-HEAD-778</v>
+      </c>
+      <c r="CI2" t="str">
+        <v>RO-316-8-300</v>
+      </c>
+      <c r="CJ2" t="str">
+        <v>Schedule Q</v>
+      </c>
+      <c r="CK2" t="str">
+        <v>No</v>
+      </c>
+      <c r="CL2" t="str">
+        <v>0.0</v>
+      </c>
+      <c r="CM2" t="str">
+        <v>450.0</v>
+      </c>
+      <c r="CN2" t="str">
+        <v>300.0</v>
+      </c>
+      <c r="CO2" t="str">
+        <v>0.0</v>
+      </c>
+      <c r="CP2" t="str">
+        <v>0.0</v>
+      </c>
+      <c r="CQ2" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="CR2" t="str">
+        <v>154.2 mm</v>
+      </c>
+      <c r="CS2" t="str">
+        <v>300#</v>
+      </c>
+      <c r="CT2" t="str">
+        <v>None</v>
+      </c>
+      <c r="CU2" t="str">
+        <v>None</v>
+      </c>
+      <c r="CV2" t="str">
+        <v>SS316</v>
+      </c>
+      <c r="CW2" t="str">
+        <v>1/2 in</v>
+      </c>
+      <c r="CX2" t="str">
+        <v>Sch 80</v>
+      </c>
+      <c r="CY2" t="str">
+        <v>2.0</v>
+      </c>
+      <c r="CZ2" t="str">
+        <v>None</v>
+      </c>
+      <c r="DA2" t="str">
+        <v>None</v>
+      </c>
+      <c r="DB2" t="str">
+        <v>None</v>
+      </c>
+      <c r="DC2" t="str">
+        <v>None</v>
+      </c>
+      <c r="DD2" t="str">
+        <v>ASME B16.5</v>
+      </c>
+      <c r="DE2" t="str">
+        <v>Weld Neck</v>
+      </c>
+      <c r="DF2" t="str">
+        <v>A105</v>
+      </c>
+      <c r="DG2" t="str">
+        <v>300#</v>
+      </c>
+      <c r="DH2" t="str">
+        <v>2.0</v>
+      </c>
+      <c r="DI2" t="str">
+        <v>A105 Steel</v>
+      </c>
+      <c r="DJ2" t="str">
+        <v>2.0</v>
+      </c>
+      <c r="DK2" t="str">
+        <v>1/2 NPT</v>
+      </c>
+      <c r="DL2" t="str">
+        <v>0.0</v>
+      </c>
+      <c r="DM2" t="str">
+        <v>None</v>
+      </c>
+      <c r="DN2" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="DO2" t="str">
+        <v>Flange Type A</v>
+      </c>
+      <c r="DP2" t="str">
+        <v>8 in</v>
+      </c>
+      <c r="DQ2" t="str">
+        <v>None</v>
+      </c>
+      <c r="DR2" t="str">
+        <v>0.0</v>
+      </c>
+      <c r="DS2" t="str">
+        <v>0.0</v>
+      </c>
+      <c r="DT2" t="str">
+        <v>0.0</v>
+      </c>
+      <c r="DU2" t="str">
+        <v>0.0</v>
+      </c>
+      <c r="DV2" t="str">
+        <v>None</v>
+      </c>
+      <c r="DW2" t="str">
+        <v>None</v>
+      </c>
+      <c r="DX2" t="str">
+        <v>None</v>
+      </c>
+      <c r="DY2" t="str">
+        <v>Bolted Sleeve</v>
+      </c>
+      <c r="DZ2" t="str">
+        <v>None</v>
+      </c>
+      <c r="EA2" t="str">
+        <v>None</v>
+      </c>
+    </row>
+  </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:EA2"/>
   </ignoredErrors>
 </worksheet>
 </file>